--- a/data/trans_orig/IP25A02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32655</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58156</t>
+          <t>59034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46771</t>
+          <t>47932</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37409</t>
+          <t>40468</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65829</t>
+          <t>66313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77307</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107471</t>
+          <t>107698</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51353</t>
+          <t>52000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74879</t>
+          <t>73631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>79522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120660</t>
+          <t>118774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37297</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>62875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74503</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105721</t>
+          <t>105515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66541</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93165</t>
+          <t>92796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>94013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123582</t>
+          <t>124383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168480</t>
+          <t>168409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209538</t>
+          <t>208276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>52081</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75293</t>
+          <t>73551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62994</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89543</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121087</t>
+          <t>121569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156181</t>
+          <t>157164</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>27124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>21588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>46207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46809</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61572</t>
+          <t>59504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64347</t>
+          <t>62044</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>99361</t>
+          <t>101195</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89982</t>
+          <t>89049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>62549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89283</t>
+          <t>88743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116930</t>
+          <t>114232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169535</t>
+          <t>168758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>40200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116517</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60752</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81663</t>
+          <t>82798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169773</t>
+          <t>172116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>34547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60257</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87087</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79291</t>
+          <t>78278</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59635</t>
+          <t>60397</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122942</t>
+          <t>122743</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155170</t>
+          <t>154067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>48668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68521</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44831</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67549</t>
+          <t>67539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99319</t>
+          <t>98778</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129876</t>
+          <t>129987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>61475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,47 +3021,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>52450</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>39525</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>65771</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>52450</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>39431</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>67295</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81984</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118595</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104370</t>
+          <t>103093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145388</t>
+          <t>144303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146619</t>
+          <t>145773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189452</t>
+          <t>188250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263033</t>
+          <t>259037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>320881</t>
+          <t>319796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>222880</t>
+          <t>222479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281840</t>
+          <t>283602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281039</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>335667</t>
+          <t>337426</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>518944</t>
+          <t>526724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>604328</t>
+          <t>604336</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>199722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>281910</t>
+          <t>286551</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>205142</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>262559</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>418968</t>
+          <t>419302</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>517365</t>
+          <t>527651</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16482</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8425</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15079</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23482</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15857</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23277</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17130</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30600</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>24100</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16966</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31549</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>14,38%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>47582</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>36651</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>58829</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>19,51%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>15,03%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23731</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16408</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34404</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>24,5%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>47009</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>36479</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>59034</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52034</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40397</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63738</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>41,33%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,08%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>39253</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32035</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47932</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,44%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>42,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53680</t>
+          <t>41871</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>50604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>92933</t>
+          <t>93905</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77531</t>
+          <t>79407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107698</t>
+          <t>108981</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42168</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31332</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60010</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43017</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35465</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>52000</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>37,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>34935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73631</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95409</t>
+          <t>85240</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79522</t>
+          <t>71595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118774</t>
+          <t>104765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>113972</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113972</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>113972</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15331</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9280</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24982</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10366</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6137</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>17869</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10022</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5934</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>17587</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>16083</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9635</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>26065</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49505</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39265</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61566</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37775</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28172</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47868</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>37229</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62875</t>
+          <t>49189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89245</t>
+          <t>86734</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>73089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105515</t>
+          <t>101651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102503</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89294</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>117959</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>78612</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67579</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>92796</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>41,56%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108763</t>
+          <t>74971</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94013</t>
+          <t>64306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124383</t>
+          <t>86088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>187374</t>
+          <t>177475</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168409</t>
+          <t>160144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208276</t>
+          <t>195582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67413</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55943</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80441</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>28,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>34,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>62380</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>52081</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>73551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>32,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76119</t>
+          <t>60896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89115</t>
+          <t>71739</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>138498</t>
+          <t>128309</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121569</t>
+          <t>112284</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>157164</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>189132</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>189132</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>189132</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>441567</t>
+          <t>417871</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441567</t>
+          <t>417871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>441567</t>
+          <t>417871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14488</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22742</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17307</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9020</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27124</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24789</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21588</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45092</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34131</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56661</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>26,79%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>34119</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>19105</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>45674</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24,56%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48236</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>23991</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59504</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>82355</t>
+          <t>77127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62044</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101195</t>
+          <t>92699</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68392</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>57437</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82457</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>70929</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43768</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>89049</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>75574</t>
+          <t>65522</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62549</t>
+          <t>55601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88743</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>146503</t>
+          <t>133914</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114232</t>
+          <t>117111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168758</t>
+          <t>150374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40369</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30522</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>53106</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>63636</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40200</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>113638</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46035</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34791</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61053</t>
+          <t>50676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>109671</t>
+          <t>80179</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82798</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172116</t>
+          <t>97662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15908</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>40029</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30709</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>49731</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>30033</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22279</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>39518</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53786</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>84863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68367</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>58367</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>80237</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67918</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>58159</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>78278</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>41,04%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>47,3%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71296</t>
+          <t>68571</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>58848</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>79314</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>139214</t>
+          <t>136938</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122743</t>
+          <t>122033</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>154067</t>
+          <t>153926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>50918</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41644</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>61460</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>24,66%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>36,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>58009</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>48668</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>70043</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>35,05%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>42,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>55979</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46261</t>
+          <t>46782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67539</t>
+          <t>66806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>113988</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>92419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129987</t>
+          <t>121381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>47629</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>36319</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>61615</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>45624</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>34761</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>61475</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>55033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>76024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>109243</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>158108</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>137594</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>179232</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>125203</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>103093</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>144303</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>166507</t>
+          <t>124058</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>145773</t>
+          <t>107799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>188250</t>
+          <t>142008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>291710</t>
+          <t>282166</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259037</t>
+          <t>257296</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>319796</t>
+          <t>310418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>291296</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>266619</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>314806</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>362</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>256711</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>222479</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>283602</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>33,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>43,33%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>309313</t>
+          <t>250935</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281346</t>
+          <t>227881</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>337426</t>
+          <t>271774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>566024</t>
+          <t>542231</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>526724</t>
+          <t>513264</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>604336</t>
+          <t>574859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>200868</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>180845</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>228946</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>227042</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>199722</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>286551</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>230524</t>
+          <t>199680</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>179973</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>221831</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>400548</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>419302</t>
+          <t>371779</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>527651</t>
+          <t>433215</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>654580</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618409</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1413374</t>
+          <t>1316310</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
